--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6731,6 +6731,410 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128369833</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Måsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>550710</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6965127</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128369832</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92657</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Måsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>550715</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6965128</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128369834</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Måsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>550692</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6965111</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128369835</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80134</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Måsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>550668</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6965039</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6736,7 +6736,7 @@
         <v>128369833</v>
       </c>
       <c r="B61" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>128369832</v>
       </c>
       <c r="B62" t="n">
-        <v>92657</v>
+        <v>92662</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>128369834</v>
       </c>
       <c r="B63" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>128369835</v>
       </c>
       <c r="B64" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B63" t="n">
-        <v>92650</v>
+        <v>80135</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R63" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B64" t="n">
-        <v>80135</v>
+        <v>92650</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R64" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6736,7 +6736,7 @@
         <v>128369833</v>
       </c>
       <c r="B61" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>128369832</v>
       </c>
       <c r="B62" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B63" t="n">
-        <v>80135</v>
+        <v>92742</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R63" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B64" t="n">
-        <v>92650</v>
+        <v>80188</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R64" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B63" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R63" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B64" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R64" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B63" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R63" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B64" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R64" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6736,7 +6736,7 @@
         <v>128369833</v>
       </c>
       <c r="B61" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>128369832</v>
       </c>
       <c r="B62" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B63" t="n">
-        <v>92742</v>
+        <v>80192</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R63" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B64" t="n">
-        <v>80188</v>
+        <v>92754</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R64" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6736,7 +6736,7 @@
         <v>128369833</v>
       </c>
       <c r="B61" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>128369832</v>
       </c>
       <c r="B62" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B63" t="n">
-        <v>80192</v>
+        <v>92756</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R63" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B64" t="n">
-        <v>92754</v>
+        <v>80194</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R64" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B63" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R63" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B64" t="n">
-        <v>80194</v>
+        <v>92756</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R64" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6736,7 +6736,7 @@
         <v>128369833</v>
       </c>
       <c r="B61" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>128369832</v>
       </c>
       <c r="B62" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B63" t="n">
-        <v>80194</v>
+        <v>92757</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R63" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B64" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R64" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6736,7 +6736,7 @@
         <v>128369833</v>
       </c>
       <c r="B61" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>128369832</v>
       </c>
       <c r="B62" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>128369834</v>
       </c>
       <c r="B63" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>128369835</v>
       </c>
       <c r="B64" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6736,7 +6736,7 @@
         <v>128369833</v>
       </c>
       <c r="B61" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>128369832</v>
       </c>
       <c r="B62" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B63" t="n">
-        <v>92784</v>
+        <v>80225</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R63" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B64" t="n">
-        <v>80221</v>
+        <v>92794</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R64" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6935,32 +6935,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369835</v>
+        <v>128369834</v>
       </c>
       <c r="B63" t="n">
-        <v>80225</v>
+        <v>92794</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550668</v>
+        <v>550692</v>
       </c>
       <c r="R63" t="n">
-        <v>6965039</v>
+        <v>6965111</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,32 +7036,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369834</v>
+        <v>128369835</v>
       </c>
       <c r="B64" t="n">
-        <v>92794</v>
+        <v>80225</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550692</v>
+        <v>550668</v>
       </c>
       <c r="R64" t="n">
-        <v>6965111</v>
+        <v>6965039</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6736,7 +6736,7 @@
         <v>128369833</v>
       </c>
       <c r="B61" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>128369832</v>
       </c>
       <c r="B62" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>128369834</v>
       </c>
       <c r="B63" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>128369835</v>
       </c>
       <c r="B64" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -6736,7 +6736,7 @@
         <v>128369833</v>
       </c>
       <c r="B61" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>128369832</v>
       </c>
       <c r="B62" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>128369834</v>
       </c>
       <c r="B63" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>128369835</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113232527</v>
+        <v>128369814</v>
       </c>
       <c r="B2" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
+          <t>Måsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551021</v>
+        <v>550902</v>
       </c>
       <c r="R2" t="n">
-        <v>6964422</v>
+        <v>6964726</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,53 +764,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113232489</v>
+        <v>113232562</v>
       </c>
       <c r="B3" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550811</v>
+        <v>550807</v>
       </c>
       <c r="R3" t="n">
-        <v>6964810</v>
+        <v>6964786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,12 +880,7 @@
         <v>113232563</v>
       </c>
       <c r="B4" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113232513</v>
+        <v>128369817</v>
       </c>
       <c r="B5" t="n">
-        <v>91795</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,37 +989,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
+          <t>Måsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550810</v>
+        <v>550902</v>
       </c>
       <c r="R5" t="n">
-        <v>6964805</v>
+        <v>6964738</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,53 +1067,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113232531</v>
+        <v>113232491</v>
       </c>
       <c r="B6" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550830</v>
+        <v>550697</v>
       </c>
       <c r="R6" t="n">
-        <v>6964725</v>
+        <v>6965278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113232562</v>
+        <v>113232527</v>
       </c>
       <c r="B7" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550807</v>
+        <v>551021</v>
       </c>
       <c r="R7" t="n">
-        <v>6964786</v>
+        <v>6964422</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113232499</v>
+        <v>120721970</v>
       </c>
       <c r="B8" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551016</v>
+        <v>550692</v>
       </c>
       <c r="R8" t="n">
-        <v>6964402</v>
+        <v>6965122</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,31 +1366,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113232488</v>
+        <v>113232513</v>
       </c>
       <c r="B9" t="n">
-        <v>91232</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4745</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550826</v>
+        <v>550810</v>
       </c>
       <c r="R9" t="n">
-        <v>6964848</v>
+        <v>6964805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,15 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113232491</v>
+        <v>120721926</v>
       </c>
       <c r="B10" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,34 +1490,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550697</v>
+        <v>550838</v>
       </c>
       <c r="R10" t="n">
-        <v>6965278</v>
+        <v>6964857</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1544,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,66 +1564,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113232564</v>
+        <v>113232994</v>
       </c>
       <c r="B11" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
+          <t>Hällmarkstallskog väster om Getingforsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550882</v>
+        <v>550968</v>
       </c>
       <c r="R11" t="n">
-        <v>6964544</v>
+        <v>6964611</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,8 +1656,9 @@
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,37 +1681,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120722034</v>
+        <v>120721939</v>
       </c>
       <c r="B12" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550741</v>
+        <v>550884</v>
       </c>
       <c r="R12" t="n">
-        <v>6965014</v>
+        <v>6964651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,37 +1778,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120721977</v>
+        <v>120721994</v>
       </c>
       <c r="B13" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550857</v>
+        <v>550782</v>
       </c>
       <c r="R13" t="n">
-        <v>6964719</v>
+        <v>6964960</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,15 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120721944</v>
+        <v>120721995</v>
       </c>
       <c r="B14" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,21 +1886,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550818</v>
+        <v>550731</v>
       </c>
       <c r="R14" t="n">
-        <v>6964940</v>
+        <v>6965197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,37 +1972,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120722026</v>
+        <v>120721996</v>
       </c>
       <c r="B15" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550883</v>
+        <v>550686</v>
       </c>
       <c r="R15" t="n">
-        <v>6964613</v>
+        <v>6965166</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,15 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120721995</v>
+        <v>120721997</v>
       </c>
       <c r="B16" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550731</v>
+        <v>550623</v>
       </c>
       <c r="R16" t="n">
-        <v>6965197</v>
+        <v>6965123</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,37 +2166,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120722038</v>
+        <v>120722078</v>
       </c>
       <c r="B17" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550751</v>
+        <v>550860</v>
       </c>
       <c r="R17" t="n">
-        <v>6965128</v>
+        <v>6964701</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,12 +2266,7 @@
         <v>120722079</v>
       </c>
       <c r="B18" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2449,15 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120721926</v>
+        <v>120722081</v>
       </c>
       <c r="B19" t="n">
-        <v>90608</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3242</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550838</v>
+        <v>550678</v>
       </c>
       <c r="R19" t="n">
-        <v>6964857</v>
+        <v>6965097</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,37 +2457,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120721974</v>
+        <v>120722083</v>
       </c>
       <c r="B20" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550924</v>
+        <v>550643</v>
       </c>
       <c r="R20" t="n">
-        <v>6964494</v>
+        <v>6965103</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,15 +2554,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120722006</v>
+        <v>113232483</v>
       </c>
       <c r="B21" t="n">
-        <v>78332</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,34 +2565,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550918</v>
+        <v>550864</v>
       </c>
       <c r="R21" t="n">
-        <v>6964579</v>
+        <v>6964934</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2723,12 +2619,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2743,31 +2639,30 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120722043</v>
+        <v>113232499</v>
       </c>
       <c r="B22" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2791,14 +2686,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550673</v>
+        <v>551016</v>
       </c>
       <c r="R22" t="n">
-        <v>6965099</v>
+        <v>6964402</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,12 +2720,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2845,31 +2740,30 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120722027</v>
+        <v>113232523</v>
       </c>
       <c r="B23" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2893,14 +2787,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550880</v>
+        <v>550820</v>
       </c>
       <c r="R23" t="n">
-        <v>6964637</v>
+        <v>6965107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,12 +2821,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2947,31 +2841,30 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120722025</v>
+        <v>120722020</v>
       </c>
       <c r="B24" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2999,10 +2892,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550878</v>
+        <v>550924</v>
       </c>
       <c r="R24" t="n">
-        <v>6964593</v>
+        <v>6964494</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,19 +2954,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120722061</v>
+        <v>120722021</v>
       </c>
       <c r="B25" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3101,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>551010</v>
+        <v>551017</v>
       </c>
       <c r="R25" t="n">
-        <v>6964437</v>
+        <v>6964500</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,15 +3051,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120722083</v>
+        <v>120722022</v>
       </c>
       <c r="B26" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,21 +3062,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3086,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550643</v>
+        <v>551002</v>
       </c>
       <c r="R26" t="n">
-        <v>6965103</v>
+        <v>6964551</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,15 +3148,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120721996</v>
+        <v>120722023</v>
       </c>
       <c r="B27" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3281,21 +3159,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3305,10 +3183,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550686</v>
+        <v>550980</v>
       </c>
       <c r="R27" t="n">
-        <v>6965166</v>
+        <v>6964541</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3367,19 +3245,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120722020</v>
+        <v>120722024</v>
       </c>
       <c r="B28" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3407,10 +3280,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550924</v>
+        <v>550897</v>
       </c>
       <c r="R28" t="n">
-        <v>6964494</v>
+        <v>6964556</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,19 +3342,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120722037</v>
+        <v>120722025</v>
       </c>
       <c r="B29" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3509,10 +3377,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550785</v>
+        <v>550878</v>
       </c>
       <c r="R29" t="n">
-        <v>6965106</v>
+        <v>6964593</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3571,15 +3439,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120722081</v>
+        <v>120722026</v>
       </c>
       <c r="B30" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,21 +3450,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3474,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550678</v>
+        <v>550883</v>
       </c>
       <c r="R30" t="n">
-        <v>6965097</v>
+        <v>6964613</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,19 +3536,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120722021</v>
+        <v>120722027</v>
       </c>
       <c r="B31" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3713,10 +3571,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>551017</v>
+        <v>550880</v>
       </c>
       <c r="R31" t="n">
-        <v>6964500</v>
+        <v>6964637</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3775,19 +3633,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120722035</v>
+        <v>120722028</v>
       </c>
       <c r="B32" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3815,10 +3668,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550741</v>
+        <v>550872</v>
       </c>
       <c r="R32" t="n">
-        <v>6965046</v>
+        <v>6964664</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3877,15 +3730,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120722002</v>
+        <v>120722030</v>
       </c>
       <c r="B33" t="n">
-        <v>78333</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3893,21 +3741,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3917,10 +3765,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>551014</v>
+        <v>550866</v>
       </c>
       <c r="R33" t="n">
-        <v>6964459</v>
+        <v>6964691</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,15 +3827,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120721994</v>
+        <v>120722031</v>
       </c>
       <c r="B34" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,21 +3838,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4019,10 +3862,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550782</v>
+        <v>550828</v>
       </c>
       <c r="R34" t="n">
-        <v>6964960</v>
+        <v>6964789</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,15 +3924,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120721939</v>
+        <v>120722032</v>
       </c>
       <c r="B35" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,21 +3935,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,10 +3959,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550884</v>
+        <v>550838</v>
       </c>
       <c r="R35" t="n">
-        <v>6964651</v>
+        <v>6964874</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,19 +4021,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120722031</v>
+        <v>120722033</v>
       </c>
       <c r="B36" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4223,10 +4056,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550828</v>
+        <v>550781</v>
       </c>
       <c r="R36" t="n">
-        <v>6964789</v>
+        <v>6964966</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,19 +4118,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120722039</v>
+        <v>120722034</v>
       </c>
       <c r="B37" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4325,10 +4153,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550760</v>
+        <v>550741</v>
       </c>
       <c r="R37" t="n">
-        <v>6965171</v>
+        <v>6965014</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,19 +4215,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120722022</v>
+        <v>120722035</v>
       </c>
       <c r="B38" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4427,10 +4250,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>551002</v>
+        <v>550741</v>
       </c>
       <c r="R38" t="n">
-        <v>6964551</v>
+        <v>6965046</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4489,37 +4312,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120721978</v>
+        <v>120722036</v>
       </c>
       <c r="B39" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4529,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550845</v>
+        <v>550771</v>
       </c>
       <c r="R39" t="n">
-        <v>6964836</v>
+        <v>6965054</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,15 +4409,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120721963</v>
+        <v>120722037</v>
       </c>
       <c r="B40" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4607,21 +4420,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4631,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551007</v>
+        <v>550785</v>
       </c>
       <c r="R40" t="n">
-        <v>6964537</v>
+        <v>6965106</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4693,19 +4506,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120722024</v>
+        <v>120722038</v>
       </c>
       <c r="B41" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4733,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550897</v>
+        <v>550751</v>
       </c>
       <c r="R41" t="n">
-        <v>6964556</v>
+        <v>6965128</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,19 +4603,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120722036</v>
+        <v>120722039</v>
       </c>
       <c r="B42" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4835,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550771</v>
+        <v>550760</v>
       </c>
       <c r="R42" t="n">
-        <v>6965054</v>
+        <v>6965171</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4897,15 +4700,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120722085</v>
+        <v>120722040</v>
       </c>
       <c r="B43" t="n">
-        <v>77980</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4913,21 +4711,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550760</v>
+        <v>550745</v>
       </c>
       <c r="R43" t="n">
-        <v>6965082</v>
+        <v>6965205</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,15 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120721952</v>
+        <v>120722041</v>
       </c>
       <c r="B44" t="n">
-        <v>91584</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5015,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550763</v>
+        <v>550721</v>
       </c>
       <c r="R44" t="n">
-        <v>6965123</v>
+        <v>6965224</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,37 +4894,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120721980</v>
+        <v>120722042</v>
       </c>
       <c r="B45" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5141,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550702</v>
+        <v>550683</v>
       </c>
       <c r="R45" t="n">
-        <v>6965128</v>
+        <v>6965148</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,15 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120722078</v>
+        <v>120722043</v>
       </c>
       <c r="B46" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5219,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550860</v>
+        <v>550673</v>
       </c>
       <c r="R46" t="n">
-        <v>6964701</v>
+        <v>6965099</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5305,37 +5088,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120721976</v>
+        <v>120722044</v>
       </c>
       <c r="B47" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550960</v>
+        <v>550653</v>
       </c>
       <c r="R47" t="n">
-        <v>6964524</v>
+        <v>6965112</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5407,19 +5185,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120722041</v>
+        <v>120722061</v>
       </c>
       <c r="B48" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5447,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550721</v>
+        <v>551010</v>
       </c>
       <c r="R48" t="n">
-        <v>6965224</v>
+        <v>6964437</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5509,19 +5282,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120722023</v>
+        <v>128369833</v>
       </c>
       <c r="B49" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5542,20 +5310,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Måsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550980</v>
+        <v>550710</v>
       </c>
       <c r="R49" t="n">
-        <v>6964541</v>
+        <v>6965127</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5579,12 +5351,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,31 +5371,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120722033</v>
+        <v>128369834</v>
       </c>
       <c r="B50" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5644,20 +5411,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Måsjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550781</v>
+        <v>550692</v>
       </c>
       <c r="R50" t="n">
-        <v>6964966</v>
+        <v>6965111</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5681,12 +5452,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5701,49 +5472,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120722030</v>
+        <v>120721965</v>
       </c>
       <c r="B51" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5753,10 +5519,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550866</v>
+        <v>550685</v>
       </c>
       <c r="R51" t="n">
-        <v>6964691</v>
+        <v>6965185</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5815,19 +5581,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120721975</v>
+        <v>113232531</v>
       </c>
       <c r="B52" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5851,14 +5612,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>551007</v>
+        <v>550830</v>
       </c>
       <c r="R52" t="n">
-        <v>6964537</v>
+        <v>6964725</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5885,12 +5646,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5905,27 +5666,26 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120721970</v>
+        <v>113232534</v>
       </c>
       <c r="B53" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5933,34 +5693,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550692</v>
+        <v>550650</v>
       </c>
       <c r="R53" t="n">
-        <v>6965122</v>
+        <v>6965261</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5987,12 +5747,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6007,62 +5767,61 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120721965</v>
+        <v>113232564</v>
       </c>
       <c r="B54" t="n">
-        <v>91962</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550685</v>
+        <v>550882</v>
       </c>
       <c r="R54" t="n">
-        <v>6965185</v>
+        <v>6964544</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6089,12 +5848,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6109,49 +5868,48 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120722044</v>
+        <v>120721974</v>
       </c>
       <c r="B55" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6161,10 +5919,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550653</v>
+        <v>550924</v>
       </c>
       <c r="R55" t="n">
-        <v>6965112</v>
+        <v>6964494</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6223,37 +5981,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120722028</v>
+        <v>120721975</v>
       </c>
       <c r="B56" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6263,10 +6016,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550872</v>
+        <v>551007</v>
       </c>
       <c r="R56" t="n">
-        <v>6964664</v>
+        <v>6964537</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6325,37 +6078,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120722042</v>
+        <v>120721976</v>
       </c>
       <c r="B57" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6113,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550683</v>
+        <v>550960</v>
       </c>
       <c r="R57" t="n">
-        <v>6965148</v>
+        <v>6964524</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,37 +6175,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120722040</v>
+        <v>120721977</v>
       </c>
       <c r="B58" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6467,10 +6210,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550745</v>
+        <v>550857</v>
       </c>
       <c r="R58" t="n">
-        <v>6965205</v>
+        <v>6964719</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6529,19 +6272,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120721979</v>
+        <v>120721978</v>
       </c>
       <c r="B59" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6569,10 +6307,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550764</v>
+        <v>550845</v>
       </c>
       <c r="R59" t="n">
-        <v>6964985</v>
+        <v>6964836</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6631,15 +6369,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120722001</v>
+        <v>120721979</v>
       </c>
       <c r="B60" t="n">
-        <v>78333</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6647,21 +6380,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6671,10 +6404,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550945</v>
+        <v>550764</v>
       </c>
       <c r="R60" t="n">
-        <v>6964543</v>
+        <v>6964985</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6733,52 +6466,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128369833</v>
+        <v>120721980</v>
       </c>
       <c r="B61" t="n">
-        <v>92803</v>
+        <v>93209</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Måsjön, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550710</v>
+        <v>550702</v>
       </c>
       <c r="R61" t="n">
-        <v>6965127</v>
+        <v>6965128</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6802,12 +6531,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6822,26 +6551,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128369832</v>
+        <v>120721981</v>
       </c>
       <c r="B62" t="n">
-        <v>92815</v>
+        <v>93209</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6862,24 +6591,20 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Måsjön, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550715</v>
+        <v>550623</v>
       </c>
       <c r="R62" t="n">
-        <v>6965128</v>
+        <v>6965120</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6903,12 +6628,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6923,44 +6648,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128369834</v>
+        <v>128369832</v>
       </c>
       <c r="B63" t="n">
-        <v>92803</v>
+        <v>93209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6974,10 +6699,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550692</v>
+        <v>550715</v>
       </c>
       <c r="R63" t="n">
-        <v>6965111</v>
+        <v>6965128</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7036,10 +6761,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128369835</v>
+        <v>113232488</v>
       </c>
       <c r="B64" t="n">
-        <v>80134</v>
+        <v>92841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7047,41 +6772,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>4745</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Måsjön, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550668</v>
+        <v>550826</v>
       </c>
       <c r="R64" t="n">
-        <v>6965039</v>
+        <v>6964848</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7105,12 +6826,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7125,15 +6846,1106 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120721952</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>550763</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6965123</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>113232524</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>550971</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6964650</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>113232489</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>550811</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6964810</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120722085</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>550760</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6965082</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120722006</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>550918</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6964579</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128369835</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Måsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>550668</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6965039</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
           <t>Annica Berglind</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
+      <c r="AX70" t="inlineStr">
         <is>
           <t>Annica Berglind</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120721944</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>550818</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6964940</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128369815</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Måsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>550901</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6964724</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128369823</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Måsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>550895</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6964823</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120722001</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>550945</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6964543</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120722002</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>551014</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6964459</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54050-2023 artfynd.xlsx
+++ b/artfynd/A 54050-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369814</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232562</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232563</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232491</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232527</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721970</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232513</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721926</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232994</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721939</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721994</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721995</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721996</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721997</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722078</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2357,6 +2442,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722079</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2454,6 +2544,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722081</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2551,6 +2646,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722083</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2652,6 +2752,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232483</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2753,6 +2858,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232499</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2854,6 +2964,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232523</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2951,6 +3066,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722020</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3048,6 +3168,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722021</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3145,6 +3270,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722022</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3242,6 +3372,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722023</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3339,6 +3474,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722024</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3436,6 +3576,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3533,6 +3678,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722026</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3630,6 +3780,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722027</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3727,6 +3882,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722028</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3824,6 +3984,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722030</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3921,6 +4086,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722031</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4018,6 +4188,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722032</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4115,6 +4290,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722033</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4212,6 +4392,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722034</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4309,6 +4494,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722035</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4406,6 +4596,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722036</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4503,6 +4698,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722037</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4600,6 +4800,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722038</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4697,6 +4902,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722039</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4794,6 +5004,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722040</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4891,6 +5106,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722041</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4988,6 +5208,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722042</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5085,6 +5310,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722043</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5182,6 +5412,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722044</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5279,6 +5514,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722061</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5380,6 +5620,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369833</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5481,6 +5726,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369834</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5578,6 +5828,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721965</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5679,6 +5934,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232531</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5780,6 +6040,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232534</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5881,6 +6146,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232564</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5978,6 +6248,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721974</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6075,6 +6350,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721975</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6172,6 +6452,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721976</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6269,6 +6554,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721977</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6366,6 +6656,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721978</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6463,6 +6758,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721979</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6560,6 +6860,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721980</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6657,6 +6962,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721981</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6758,6 +7068,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369832</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6859,6 +7174,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232488</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6956,6 +7276,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721952</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7057,6 +7382,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232524</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7158,6 +7488,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232489</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7255,6 +7590,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722085</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7352,6 +7692,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722006</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7453,6 +7798,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369835</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7550,6 +7900,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721944</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7651,6 +8006,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369815</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7752,6 +8112,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369823</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7849,6 +8214,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722001</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7946,8 +8316,89 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>